--- a/demo/newsapp/news_data/AAPL.xlsx
+++ b/demo/newsapp/news_data/AAPL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,38 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>標題</t>
+          <t>title</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>內容</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>連結</t>
+          <t>link</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>正負分析</t>
+          <t>source</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>來源</t>
+          <t>positive_negative_analysis</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sentiment_score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>impact_scope</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>reasoning_summary</t>
         </is>
       </c>
     </row>
@@ -471,12 +496,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -503,12 +549,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -535,12 +602,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -567,12 +655,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -599,12 +708,33 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -631,12 +761,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -663,12 +814,33 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -695,12 +867,33 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -727,12 +920,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -759,12 +973,33 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -791,12 +1026,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -823,12 +1079,33 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -855,12 +1132,33 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -887,12 +1185,33 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -919,12 +1238,33 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -951,12 +1291,33 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -983,12 +1344,33 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1397,33 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1450,33 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1503,33 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1556,33 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1609,33 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1662,33 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1715,33 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1768,33 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1821,33 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1874,33 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1927,33 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1980,33 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1399,12 +2033,33 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1431,12 +2086,33 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1463,12 +2139,33 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1495,12 +2192,33 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1527,12 +2245,33 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1559,12 +2298,33 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1591,12 +2351,33 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1623,12 +2404,33 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1655,12 +2457,33 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1687,12 +2510,33 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1719,12 +2563,33 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1751,12 +2616,33 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1783,12 +2669,33 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1815,12 +2722,33 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1847,12 +2775,33 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1879,12 +2828,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1911,12 +2881,33 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1943,12 +2934,33 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -1975,12 +2987,33 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2007,12 +3040,33 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2039,12 +3093,33 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2071,12 +3146,33 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2103,12 +3199,33 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2135,12 +3252,33 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2167,12 +3305,33 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2199,12 +3358,33 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2231,12 +3411,33 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2263,12 +3464,33 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2295,12 +3517,33 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2327,12 +3570,33 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2359,12 +3623,33 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2391,12 +3676,33 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2423,12 +3729,33 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2455,12 +3782,33 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2487,12 +3835,33 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2519,12 +3888,33 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2551,12 +3941,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2583,12 +3994,33 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2615,12 +4047,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2647,12 +4100,33 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2679,12 +4153,33 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2711,12 +4206,33 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2743,12 +4259,33 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2775,12 +4312,33 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2807,12 +4365,33 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2839,12 +4418,33 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2871,12 +4471,33 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2903,12 +4524,33 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2935,12 +4577,33 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2967,12 +4630,33 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -2999,12 +4683,33 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3031,12 +4736,33 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3063,12 +4789,33 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3095,12 +4842,33 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3127,12 +4895,33 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3159,12 +4948,33 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3191,12 +5001,33 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3223,12 +5054,33 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3255,12 +5107,33 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>
@@ -3287,12 +5160,33 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>鉅亨網-美股-AAPL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>鉅亨網-美股-AAPL</t>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Agent 呼叫失敗，請檢查 API Key 或網路連線。</t>
         </is>
       </c>
     </row>

--- a/demo/newsapp/news_data/AAPL.xlsx
+++ b/demo/newsapp/news_data/AAPL.xlsx
@@ -1,107 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Infinity\mydjango\demo\newsapp\news_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4C5050-3EC4-4455-AB87-6552BA4DEFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="11520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="2" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
-  <si>
-    <t>鉅亨網-美股-AAPL</t>
-  </si>
-  <si>
-    <t>標題</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>內容</t>
-  </si>
-  <si>
-    <t>連結</t>
-  </si>
-  <si>
-    <t>正負分析</t>
-  </si>
-  <si>
-    <t>來源</t>
-  </si>
-  <si>
-    <t>〈美股盤後〉美光跌近6%記憶體族群拖累科技股 那指標普連二跌</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
-    <t>美股 〈美股盤後〉美光跌近6%記憶體族群拖累科技股 那指標普連二跌 鉅亨網編譯陳又嘉 綜合外電 2026-05-19 05:41 美國股市周一 (18 日) 多收低，受科技股走弱拖累，其中記憶體晶片股跌勢尤其明顯。投資人持續關注油價與公債殖利率走勢，同時等待中東衝突的進一步發展。 標普500與那斯達克綜合指數連續第二個交易日下跌(圖：Reuters/TPG) 標普 500 與 那斯達克綜合指數 皆連續第二個交易日下跌。 道瓊工業指數 則上漲 159.95 點，漲幅 0.32%。 ‌ 記憶體晶片類股遭遇拋售潮，起因於希捷科技 (Seagate Technology)( STX-US ) 執行長在摩根大通 (JPMorgan) 會議上表示，新建工廠「耗時太久」。該公司股價重挫近 7%，並拖累同業美光 (Micron Technology)( MU-US ) 下跌近 6%。市場擔憂記憶體產業產能不足，恐無法滿足快速成長的需求，進一步加劇賣壓。 除美光與希捷科技外，威騰電子 (Western Digital)( WDC-US ) 下跌 4.8%，Sandisk 下跌 5.3%。其他 AI 概念股也同步走弱，包括輝達 (Nvidia)( NVDA-US ) 與博通 (Broadcom)( AVGO-US ) 皆下跌約 1%。 這波跌勢發生之際，美股先前才剛創下新高。標普 500 與 那斯達克 上周刷新歷史紀錄， 道瓊指數 也一度重返 50,000 點關卡。 不過，上周五全球主權債殖利率攀升，使主要指數承壓。美國 30 年期公債殖利率升至約一年高點， 10 年期公債殖利率 也維持高檔。英國 30 年期公債殖利率升至 1990 年代末以來最高，日本長天期公債殖利率同樣攀升。 伊朗與美國的緊張局勢仍未緩解，油價維持高檔，市場對衝突後續發展仍缺乏明確方向。西德州中級原油 (WTI) 期貨上漲約 3%，收在每桶 108.66 美元； 布蘭特原油 (Brent) 則上漲逾 2%，收在每桶 112.10 美元。 不過，在美國總統川普於 Truth Social 發文表示，原定周二對伊朗的攻擊行動將暫緩後，油價漲勢有所降溫。川普指出，卡達、沙烏地阿拉伯與阿拉伯聯合大公國領導人要求暫停行動，因為目前「正進行嚴肅談判」，可能達成一項「美國可接受」的協議。 此外，上周公布的通膨數據高於預期，讓市場認為聯準會 (Fed) 短期內降息的可能性大幅降低。 根據芝商所 (CME)FedWatch 工具，交易員目前預估聯準會今年底前升息 25 個基點的機率為 37.8%，反映市場消化上周高於預期的通膨數據。 全球市值最高公司輝達將於周三公布財報。市場對其表現抱持高度期待，該公司股價自 3 月低點以來已大幅反彈，而 費城半導體 指數今年也因 AI 晶片需求強勁而大漲。 全球最大零售商沃爾瑪 (Walmart)( WMT-US ) 本周也將公布財報，市場將藉此觀察美國消費者在高油價與整體通膨壓力下的消費狀況。 美股周一 (18 日) 主要指數表現： 道瓊指數 上漲 159.95 點，或 0.32%，收 49,686.12 點。 那斯達克 指數下跌 134.41 點，或 0.51%，收 26,090.73 點。 S&amp;P 500 指數下跌 5.45 點，或 0.074%，收 7,403.05 點。 費城半導體 指數下跌 285.95 點，或 2.47%，收 11,302.52 點。 NYSE FANG + 指數下跌 139.44 點，或 0.81%，收 17,106.12 點。 標普 11 大類股中，資訊科技類股跌幅最大，其中晶片股為主要拖累，能源類股則表現最佳。(圖片：finviz) 焦點個股 NYSE FANG + 科技五天王漲跌互見。Meta ( META-US ) 下跌 0.49%；蘋果 ( AAPL-US ) 下跌 0.8%；Alphabet ( GOOGL-US ) 上漲 0.04%；微軟 ( MSFT-US ) 上漲 0.38%；亞馬遜 ( AMZN-US ) 上漲 0.27%。 費半 成分股倒一片。輝達 ( NVDA-US ) 下跌 1.33%；博通 ( AVGO-US ) 下跌 1.05%；美光 ( MU-US ) 下跌 5.95%；高通 ( QCOM-US ) 上漲 1.07%；應用材料 ( AMAT-US ) 下跌 5.28%；德儀 ( TXN-US ) 下跌 0.7%；AMD ( AMD-US ) 下跌 0.73%。 台股 ADR 多收低。台積電 ADR ( TSM-US ) 下跌 2.08%；日月光 ADR ( ASX-US ) 下跌 6.39%；聯電 ADR ( UMC-US ) 下跌 0.47%；中華電信 ADR ( CHT-US ) 上漲 0.</t>
-  </si>
-  <si>
-    <t>https://news.cnyes.com/news/id/6462566</t>
-  </si>
-  <si>
-    <t>中性</t>
-  </si>
-  <si>
-    <t>川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>美股 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單 鉅亨網編輯林羿君 2026-05-18 22:30 根據最新的財產申報資料，美國總統川普在今年第一季的投資標的中，除了納入輝達 ( NVDA-US ) 、亞馬遜 ( AMZN-US ) 與蘋果 ( AAPL-US ) 等股市巨頭之外，他還入股了一家市值達 6 億美元的迴轉壽司連鎖品牌。 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單。(圖:shutterstock) 川普於 2 月 2 日買進美國藏壽司 ( KRUS-US ) 的股票，交易金額介於 100 萬至 500 萬美元之間。該餐飲集團是由日本藏壽司（Kura Sushi）所控股。 ‌ 與歷任總統的做法不同，川普並未選擇處分自身資產，也未將其移交給獨立監理人進行盲目信託。 申報文件揭露，川普或其投資顧問在首季進行了超過 3,700 筆交易，這使得外界對於川普政府可能涉及「利益衝突」的疑慮再度升溫。 對此，川普集團發言人表示，總統的所有資產均由第三方金融機構獨立管理，並全權負責所有投資決策，不論是川普本人、其家人或集團，皆未參與任何交易決定。 這筆出人意料的投資在日本引發了廣泛熱議，許多網友紛紛在社群平台 X 上猜測，川普本人到底有沒有吃過握壽司。 三菱日聯 eSmart 證券市場分析師山田勉指出，美國藏壽司的營運表現一直以來都極為強勁，而川普入股的消息，可能會進一步刺激東京股市的散戶大舉買進藏壽司股票。 受此消息激勵，在東京掛牌的藏壽司股價於週一 (18 日) 盤中一度大漲 5.4%，創下 2025 年 6 月以來最大的單日盤中漲幅。 而根據該公司的年度有價證券報告，截至去年 10 月底，母公司日本藏壽司持有美國藏壽司約 67% 的表決權。 主動選股績效夯！專家配置一鍵打包 掌握全球財經資訊 點我下載APP ‌ 文章標籤 川普投顧 川普持股 藏壽司 迴轉壽司 TOP 更多 相關行情 台股首頁 我要存股 輝達 222.32 -1.33 % 亞馬遜 264.86 +0.27 % 蘋果 297.84 -0.80 % Kura Sushi USA Inc - Class A 51.07 +1.21 % 更多 延伸閱讀 美以很快再發動攻擊？川普威脅伊朗恐「將一無所有」伊方：美方毫無實質讓步 川普發文警告：如果伊朗不迅速行動 將一無所有 川普警告時間不多 美以密談聯手空襲伊朗 ‌ 鉅亨講座 看更多 講座 公告 上一篇 搶攻AI資料中心商機！NextEra砸668億美元收購Dominion 創電力業紀錄 下一篇 債市已發出警告 但股市投資者尚未計價通膨飆升的風險 0</t>
-  </si>
-  <si>
-    <t>https://news.cnyes.com/news/id/6462385</t>
-  </si>
-  <si>
-    <t>瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機</t>
-  </si>
-  <si>
-    <t>美股 瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機 鉅亨網編譯段智恆 2026-05-18 20:10 蘋果 ( AAPL-US ) 向來以高單價、高毛利產品聞名，但在全球消費電子成本持續攀升之際，蘋果近年卻成功在平價裝置市場殺出新路，而背後一項關鍵策略，如今也逐漸浮上檯面：將原本可能報廢的「次級晶片」重新利用，轉化為獲利來源。 瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機(圖：REUTERS/TPG) 根據《華爾街日報》(WSJ)報導，蘋果近期推出售價 599 美元的入門筆電 MacBook Neo，上市後銷售表現優於預期，成為市場熱門產品。不過，支撐這款新產品的核心晶片，並非全新設計，而是兩年前首次搭載於 iPhone 16 Pro 的 A18 Pro 晶片，只是其中圖形處理器 (GPU) 由原本 6 核心降為 5 核心。 ‌ 這意味著，部分在生產過程中未完全達到最高規格、但仍可正常運作的晶片，經過關閉瑕疵核心後，仍能被重新部署至不同產品線，從原本旗艦手機轉向價格更親民的筆電產品。 報導指出，這種做法在半導體業被稱為「分級晶片」(Binned Chips)，透過將晶片依性能分級，區分為高、中、低不同等級，再搭配不同產品定位出售，類似航空座位、飯店房型或鑽石分級的商業模式。 分析人士指出，蘋果近年已將這項原本用於降低報廢率的供應鏈策略，進一步發展為產品設計核心，不僅有效降低成本，也讓蘋果能更精準切分高階與入門市場，吸引更多原本可能選擇 Chromebook、Windows PC 或 Android 手機的消費者。 根據《華爾街日報》分析蘋果近 200 份技術文件，自 2021 年以來，蘋果至少已有 6 款 A 系列晶片，在旗艦 iPhone 首發後，再以少一個 GPU 核心的版本導入較低價產品，包括 iPhone 17e、iPhone Air，以及最新的 MacBook Neo。 Neo 熱銷甚至已消耗完原本庫存的次級晶片。知情人士透露，蘋果近期已向台積電 ( TSM-US )( 2330-TW ) 追加 A18 Pro 晶片訂單，以維持 Neo 產線供應，顯示市場需求遠超預期。 不過，隨著人工智慧 (AI) 晶片需求爆發，全球先進製程產能日益吃緊，台積電供應壓力也同步升高。天風國際證券分析師郭明錤指出，蘋果過去在晶片供應上的彈性優勢正在縮小，相關壓力已開始浮現。蘋果執行長庫克近期也坦言，晶片短缺正影響產品供貨，目前官網顯示 MacBook Neo 出貨時間已延長至 1 至 2 周。 主動選股績效夯！專家配置一鍵打包 免費體驗5萬美元模擬交易 投資全球資產 掌握全球財經資訊 點我下載APP ‌ 文章標籤 蘋果 Apple MacBook Neo A18 Pro GPU 晶片 台積電 庫克 郭明錤 AI 人工智慧 筆電 iPhone 半導體 供應鏈 消費電子 科技 產業 TOP 更多 相關行情 台股首頁 我要存股 台積電 2240 -1.10 % 蘋果 297.84 -0.80 % 台積電ADR 395.95 -2.08 % 更多 延伸閱讀 川普自曝入股英特爾談判內幕：早知道應該多要一點 2兆美元值不值？SpaceX IPO背後的FOMO心理學 輝達法說不只看財報！市場更想聽黃仁勳談川普與對中晶片出口 Meta裁員不只是省錢！祖克柏AI重押正改變矽谷生態 ‌ 鉅亨講座 看更多 講座 公告 上一篇 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單 下一篇 債券拋售加劇 美股恐迎「首波實質修正」威脅AI漲勢 0</t>
-  </si>
-  <si>
-    <t>https://news.cnyes.com/news/id/6462511</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,92 +414,695 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>0</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>標題</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>內容</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>正負分析</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>市場</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>信心度</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>影響範疇</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>分析摘要</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【量大強漲股整理】今天是跌假的嗎？！散戶還在逃，【5351鈺創】狂飆+80%！破解台股5大選股密碼！</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>台股 【量大強漲股整理】今天是跌假的嗎？！散戶還在逃，【5351鈺創】狂飆+80%！破解台股5大選股密碼！ 鉅亨研報 2026-07-07 17:16 今天是跌假的嗎？！散戶還在逃，【5351 鈺創】狂飆 + 80%！破解台股 5 大選股密碼！ 【量大強漲股整理】今天是跌假的嗎？！散戶還在逃，【5351鈺創】狂飆+80%！破解台股5大選股密碼！(圖:shutterstock) ‌ 影片中分享給你知道 （按讚訂閱打開小鈴鐺） 再來看一下今天的台股! 加權指數 今日開低走低，終場下跌 1077.28 點，收在 45479.11，成交量 11696.27 億。 觀察三大法人今天籌碼動向，外資賣超 547.31 億元，投信買超 87.73 億元，自營商賣超 487.33 億元，三大法人合計賣超 946.91 億元，其中，外資、自營商連賣四日，投信則連買十一日共買超 1017.41 億元。 美股周一全面走強， 道瓊工業指數 上漲 0.29%，再創歷史收盤新高， 那斯達克 指數勁揚 1.12%， 標普 500 指數 上漲 0.72%， 費城半導體 指數更大漲 2.17%，顯示市場資金持續回流 AI 與半導體族群，也為台股電子權值股帶來正向激勵，( AVGO-US ) 博通，宣布與 ( AAPL-US ) 蘋果，簽署延續至 2031 年的 ASIC 晶片合作協議，激勵股價同步走揚，也推升晶圓代工夥伴 ( TSM-US ) 台積電 ADR 大漲 4.06%，市場同時聚焦 AI 供應鏈動態，雖然研調機構指出 ( NVDA-US ) 輝達，次世代 Rubin Ultra 平台恐延後推出，但輝達隨即駁斥相關傳聞，強調產品開發時程未有改變，終場股價仍收紅，此外 ( AMD-US ) 超微，獲高盛調升目標價後強漲逾 6%，( CRDO-US )Credo，及 ( ALAB-US )Astera Labs，也分別大漲近 10% 及 6%，高速互連與資料中心概念股持續受到資金追捧，美股科技股維持多頭格局。 亞洲科技股今日普遍承受賣壓， 加權指數 今日開低走低，主因三星電子公布優於市場預期的財報後，股價反而重挫，引發市場對記憶體需求及短線評價過高的疑慮，也使南韓半導體族群同步回檔，事實上，近期亞洲股市累積漲幅已大，獲利了結賣壓自然增加，因此修正並非台股獨有，而是區域市場同步整理的一環，台股今日開低後一度大漲逼近 47000 點關卡，但隨後賣壓湧現，盤中由紅翻黑，高低點震盪逾千點，終場下跌 1077.28 點，收在 45479.11，成交量 11696.27 億，顯示市場情緒與短線籌碼調節同步發酵，不過電子權值股仍大致守穩，買盤並未全面撤出，多方架構尚未遭到破壞，整體仍維持震盪偏多格局。 市場接下來將聚焦本周公布的聯準會會議紀錄、美國第二季企業財報，以及美國通膨與利率政策變化，相關結果將牽動市場對降息時程及企業獲利展望的預期，同時，國內則將迎來 ( 2408-TW ) 南亞科，與 ( 3008-TW ) 大立光，法說會以及 6 月營收陸續公布，將成為影響資金輪動的重要觀察指標，若 AI 伺服器、高效能運算及先進封裝需求持續升溫，將有助支撐半導體供應鏈後續表現，相關族群仍是市場資金布局重心，展望下半年，市場對台股看法持續轉趨樂觀，在 AI 需求持續爆發、企業獲利上修及政策利多支撐下，法人普遍認為上市櫃企業全年獲利年增率可望突破四成，成為推升台股的重要基本面支柱，目前內外資機構紛紛調高台股目標指數，其中凱基投顧預估高點可望挑戰 50000 點，樂觀情境甚至上看 55000 點，台新投顧預估 53176 點，群益投顧預估 53000 點，高盛證券預估 51000 點，兆豐投顧、宏遠投顧及國泰世華銀行則同步看好 50000 點，顯示 50000 點已逐漸成為市場主流共識，除了企業獲利持續成長外，內資資金動能同樣是推升行情的重要力量，雖然台股股價淨值比已來到歷史高檔，部分外資持續獲利了結，但在 ETF 規模持續攀升、融資餘額增加以及國內長線資金穩定流入下，內資已成為支撐市場的重要買盤，整體而言，只要 ( 2330-TW ) 台積電，等權值股維持穩定，加上成交量能逐步放大至 20 日均量約 1.36 兆元水準，台股在震盪整理後，仍有機會再次挑戰 48218 點歷史高點，並延續中長期偏多格局。 權值股方面，( 2330-TW ) 台積電，下跌 0.81%，收在 2440 元，花旗最新看好台積電後市表現，將目標價由 2,875 元大幅調升至 3,800 元，並重申「買進」評等，主因 AI 需求持續升溫，帶動先進製程與先進封裝訂單能見度提升，法人預期，2 奈米、3 奈米製程需求強勁，晶圓代工價格明年仍有調漲空間，加上 CoWoS、SoIC 等先進封裝產能持續擴充，將進一步強化獲</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6525646</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>大盤單日重挫且散戶恐慌，特定個股卻呈極端漲幅，顯示資金集中且短線投機情緒高漲。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LG Innotek股價回檔近49% 市場仍看好下半年iPhone新機與FC-BGA成長動能</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>美股 LG Innotek股價回檔近49% 市場仍看好下半年iPhone新機與FC-BGA成長動能 優分析 Uanalyze 2026-07-07 14:00 2026年07月07日（優分析／產業數據中心報導）⸺ 南韓電子零組件廠LG Innotek近期股價大幅回檔，主因市場擔憂蘋果Apple( AAPL-US )價格政策變化，可能影響後續iPhone需求。不過，韓國券商普遍認為，隨著下半年iPhone新機推出、Pro系列占比提升，以及半導體基板業務成長，LG Innotek中長期成長動能仍未改變。 根據韓國交易所資料，LG Innotek股價7日收783,000 韓元 ，較6月1日收盤高點1,530,000 韓元 下跌約49%。 ‌ LG Innotek是LG集團旗下電子零組件製造商，產品涵蓋智慧手機、半導體、汽車電子、顯示器及物聯網（IoT）等應用。其中，光學解決方案是最大營收來源，主要供應智慧手機相機模組、3D感測模組及光學防手震（OIS）致動器；半導體基板業務則包括FC-BGA、FC-CSP、RF-SiP等高階封裝基板。此外，公司也積極布局車用電子，提供車載通訊、自動駕駛、電動車及車燈模組等產品，近年更持續擴大AI伺服器、高效能運算（HPC）及資料中心相關高階基板布局，降低對智慧手機市場的依賴。 市場認為，近期股價修正主要受到蘋果產品漲價疑慮影響。由於蘋果近期調高MacBook與iPad售價，投資人擔心未來iPhone也可能漲價，進而壓抑終端需求。 不過，分析人士指出，iPhone是蘋果營收核心產品，蘋果不太可能採取足以明顯傷害出貨量的大幅漲價策略。供應鏈調查也顯示，下半年iPhone生產計畫目前並未出現明顯變化，2028年前出貨展望仍維持穩健。 券商也預期，下半年iPhone新機效應將成為LG Innotek獲利回升主因。隨著高階機型比重提高，LG Innotek光學解決方案事業可望受惠，帶動相機模組等高附加價值產品出貨增加。 此外，半導體基板業務也被視為下一階段成長引擎。LG Innotek目前RF-SiP、FC-CSP等基板產品維持高稼動率，而FC-BGA業務則受惠AI資料中心投資擴大，客戶供應討論轉趨積極。 市場人士指出，FC-BGA正逐步從AI加速器、伺服器CPU、網路交換器延伸至通訊衛星等應用，主要客戶也開始討論長期供應合約（LTA），使中長期需求與擴產規劃更為明確。 若FC-BGA訂單自今年下半年起加速落地，並在2027年進入量產，將有助LG Innotek降低對手機零組件的依賴，讓營收結構從行動裝置逐步擴大至半導體、伺服器與通訊市場。 ※ 本文經「優分析」授權轉載，原文出處: 原文連結 ※ 免責聲明：文中所提的個股、基金、期貨商品內容僅供參考，並非投資建議，投資人應獨立判斷，審慎評估風險。 ‌ 文章標籤 IC載板 優分析 更多 延伸閱讀 南電法說會｜需求強勁，首季營收年增逾3成，ABF載板供需缺口恐擴大至2028年 AI伺服器需求不斷上修Ibiden股價飆新高、ASIC成下一波載板引擎 ‌ 鉅亨講座 看更多 講座 公告 上一篇 伊朗正式解除石化產品出口禁令 化工、聚合物出口恢復正常 下一篇 分析師示警：半導體股「高速列車」恐出軌 AI長線趨勢不變但波動風險升高 0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6525307</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>受惠下半年蘋果iPhone新機推出及FC-BGA基板業務成長，中長期成長動能依然穩健。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>科技7巨頭熄火？華爾街：現在正是逢低布局好時機</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>美股 科技7巨頭熄火？華爾街：現在正是逢低布局好時機 鉅亨網編輯林羿君 2026-07-07 12:00 2026 年以來，市場俗稱的「科技七巨頭」（Magnificent Seven）表現平淡，但部分華爾街機構認為，這些大型科技股有望迎來反彈。 科技七巨頭包括輝達 ( NVDA-US ) 、Alphabet 公司 (A)( GOOGL-US ) 、Meta( META-US ) 、微軟 ( MSFT-US ) 、特斯拉 ( TSLA-US ) 、蘋果 ( AAPL-US ) 與亞馬遜 ( AMZN-US ) 。這些企業與 AI 投資熱潮高度連動，自 2022 年底以來股價大幅上漲。然而，今年以來整體表現相對疲弱。 ‌ 美股七巨頭 ETF( MAGS-US ) 自今年初以來幾乎持平，反觀半導體類股大幅上漲， 標普 500 指數 則已錄得雙位數漲幅。 近幾週市場的主流論調是，投資人對超大型雲端服務商（Hyperscalers）持續大舉投入 AI 的效益愈來愈存疑，因此資金轉向獲利成長更強勁的產業與個股。 不過，這樣的市場敘事可能正開始改變。部分華爾街機構指出，隨著晶片股漲勢出現震盪，超大型雲端服務商有望重新受到投資人青睞。 以下為看好科技七巨頭與超大型雲端服務商的主要華爾街機構及其理由。 摩根士丹利 摩根士丹利 ( MS-US ) 週一 (6 日) 發布報告指出，預期市場資金將逐步由半導體股回流至超大型雲端服務商，因為市場將開始獎勵那些在 AI 資本支出上展現更高紀律的企業。 該行美國首席股票策略師 Mike Wilson 表示：「超大型雲端服務商與半導體股之間近期出現的劇烈表現分歧，恐怕難以持續，因為後者的成長終究仍仰賴前者的投資。」 Wilson 補充指出，每當這類股價走勢分歧告一段落，兩類股票往往會出現反向輪動，而一旦超大型雲端服務商進一步收斂資本支出計畫，便可能成為這波資金輪動的催化劑。 高盛 高盛 ( GS-US ) 美國首席股票策略師 Ben Snider 於 6 月底接受《Business Insider》訪問時表示，超大型雲端服務商目前估值具備吸引力。 他指出，這些公司的本益比已回落至與 2020 年 3 月疫情引發股市重挫後觸底時，以及 2022 年 10 月聯準會大舉升息、 標普 500 指數 自高點回落約 25% 時相近的水準。 Snider 表示，高盛近期已開始與客戶討論增加科技七巨頭相關部位。 Empower Investments Empower Investments 首席投資策略師 Marta Norton 也將這類個股視為其最具信心的投資首選，尤其是與 AI 題材連動度極高的輝達、亞馬遜、微軟、Alphabet 與 Meta。 她認為，相較於整體 標普 500 指數 ，這些科技巨頭目前的估值已來到歷史相對低點。 orton 強調，投資人現在買進這些個股的估值，基本上就跟買進廣泛美股大盤的估值相去不遠；她更直言，即使自己未來十年都無法盯盤，這些巨頭絕對會是她希望保留在投資組合中的核心標的。 8/11掌握美股科技成長浪潮免費講座 掌握全球財經資訊 點我下載APP ‌ 文章標籤 科技7巨頭 AI股 AI權值股 華爾街 Magnificent Seven 美股科技股 科技股 更多 相關行情 台股首頁 我要存股 S&amp;P 500 7491.02 -0.62 % Alphabet公司(A) 367.455 +0.27 % 摩根士丹利 222 -0.05 % 亞馬遜 245.63 +0.60 % 蘋果 312.175 -0.16 % 特斯拉 403.21 -3.95 % 微軟 389.7601 +0.78 % 輝達 196.03 +0.25 % 高盛集團 1042.8321 -1.18 % Meta平台 616.06 +2.63 % 美股七巨頭ETF 66.29 +0.02 % Meta平台 616.06 +2.63 % 更多 延伸閱讀 美股今明迎300億美元「機械式賣壓」 台韓科技股也需警戒 看好AI卻嫌貴 散戶矛盾心態曝光：伺機抄底這類科技股 晶片股觸頂了？華爾街罕見喊話：可續抱、別加碼 華爾街再喊多！富國銀行上調標普500目標至7950點 ‌ 鉅亨講座 看更多 講座 公告 上一篇 傳奇投資大師喊「我正在賣」 警告AI泡沫：別相信華爾街 下一篇 博通領軍晶片股走高 美股再創高 道瓊登上53,055點 0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6524487</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>華爾街認為科技七巨頭近期股價平淡僅為修正，其與AI熱潮高度連動之基本面依然穩健，為逢低佈局迎接反彈的良機。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>蘋果延長與博通晶片合作至2031年 鞏固無線通訊晶片供應鏈</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>美股 蘋果延長與博通晶片合作至2031年 鞏固無線通訊晶片供應鏈 優分析 Uanalyze 2026-07-07 11:30 2026年07月07日（優分析／產業數據中心報導）⸺ 蘋果Apple( AAPL-US )已與博通Broadcom( AVGO-US )延長晶片供應合作至2031年，擴大雙方既有的長期合作協議，涵蓋多項客製化晶片的共同開發與供應，進一步鞏固蘋果核心產品的無線通訊晶片供應鏈。 蘋果多年來一直是博通最重要的客戶之一，市場普遍估計，蘋果約貢獻博通全年營收約20%，雙方長期合作也成為博通穩定成長的重要支柱。 ‌ 近年來，蘋果持續推動自研晶片策略，包括推出自家設計的C1與C1X行動通訊基頻晶片，逐步降低對外部供應商的依賴。不過，在無線連接及射頻（RF）技術領域，博通仍是蘋果不可或缺的合作夥伴。 目前，博通持續為蘋果提供多項客製化射頻元件，以及Wi-Fi、Bluetooth等無線連接晶片，並供應其他網路通訊半導體，廣泛應用於iPhone、iPad及Mac等產品，支撐裝置的無線通訊與網路連線功能。 此次合作延長至2031年，反映即使蘋果積極發展自研晶片，短期內仍將持續仰賴博通在無線通訊與射頻技術的實力。 ※ 本文經「優分析」授權轉載，原文出處: 原文連結 ※ 免責聲明：文中所提的個股、基金、期貨商品內容僅供參考，並非投資建議，投資人應獨立判斷，審慎評估風險。 8/11掌握美股科技成長浪潮免費講座 掌握全球財經資訊 點我下載APP ‌ 文章標籤 IC設計 半導體 優分析 更多 相關行情 台股首頁 我要存股 蘋果 312.175 -0.16 % 博通 368.81 -1.36 % 更多 延伸閱讀 超豐電子接手安森美菲律賓廠擴大全球封測版圖 分析師示警：半導體股「高速列車」恐出軌 AI長線趨勢不變但波動風險升高 英特爾調漲CPU價格 PC售價短期恐維持高檔 AI基礎建設成本同步攀升 AI掀記憶體荒 SEMI致函美政府：勿干預價格、籲延長租稅優惠 ‌ 鉅亨講座 看更多 講座 公告 上一篇 高貝塔動量籃子兩日崩18%！高盛看到「逢低買入」跡象：AI交易「夏日低迷」可轉入防禦性資產 下一篇 博通領軍晶片股走高 美股再創高 道瓊登上53,055點 0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6525026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>合約延長至2031年，確保蘋果無線晶片長期穩定供應，並穩固博通營收基盤，對雙方具長期正面戰略效益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>英特爾調漲CPU價格 PC售價短期恐維持高檔 AI基礎建設成本同步攀升</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>美股 英特爾調漲CPU價格 PC售價短期恐維持高檔 AI基礎建設成本同步攀升 優分析 Uanalyze 2026-07-07 11:30 2026年07月07日（優分析／產業數據中心報導）⸺ 在DRAM與NAND Flash價格持續上漲後，中央處理器（CPU）也正式加入漲價行列。英特爾Intel( INTC-US )證實，已調高部分消費級及伺服器級CPU建議售價，市場預期將進一步推升企業AI基礎建設成本，並使個人電腦（PC）價格短期內維持高檔。 根據市場消息，此次調價主要涵蓋Core Ultra 200S Plus消費級處理器，以及部分Xeon 6與Xeon 8000系列伺服器處理器。對於漲價原因，英特爾表示，價格調整是基於市場環境變化，以及持續檢視供應鏈與相關成本後所做出的決策。 ‌ 業界人士指出，伺服器級CPU價格調漲將直接提高企業建置AI資料中心及運算基礎設施的成本，而消費級CPU價格上升，則可能進一步反映在PC終端售價。 IDC表示，在目前市場環境下，具備供應鏈管理、服務能力及價格控管優勢的廠商，將更有能力因應原物料價格波動、技術升級及市場不確定性。該機構預估，PC價格短期內仍將維持高檔，中國市場預計需5至6個季度才能恢復穩定，2027年後市場才有望逐步回歸正常。 從產品來看，此次價格調整涵蓋Arrow Lake系列部分消費級處理器，以及Xeon伺服器產品線。其中，Xeon 8000系列「Emerald Rapids」部分型號建議售價已高於2023年上市時的價格；不過，Arrow Lake產品並非全面漲價，部分入門機型售價仍低於初始定價。 市場關注的是，CPU成本上升正與其他關鍵零組件價格上漲同步發生，可能持續推高終端電子產品售價。 今年6月底，蘋果Apple( AAPL-US )已調漲MacBook、iPad及多項硬體產品全球售價，平均漲幅約20%，主要反映記憶體及儲存晶片成本增加。隨後，微軟Microsoft( MSFT-US )也宣布，由於關鍵零組件成本持續攀升，Xbox遊戲主機售價同步調高。中國多家PC品牌業者近期亦展開新一波價格調整。 分析人士認為，上游零組件價格上漲、AI PC規格持續升級，以及供應鏈調整等因素，正共同推升PC產品價格。 值得注意的是，伺服器處理器價格調整幅度遠高於消費性產品。其中，高階Xeon 6「Granite Rapids」系列雖然目前售價仍略低於2024年上市時的水準，但相較英特爾2025年調降價格後的低點，部分型號售價已翻倍。另一方面，Xeon 8000系列「Emerald Rapids」部分產品的建議售價甚至高於2023年上市時的價格，最高調漲超過1,300美元。 在AI資料中心需求持續擴張下，分析師指出，伺服器晶片價格劇烈波動將直接影響企業採購成本，未來AI基礎建設投資壓力可能進一步升高。 另一方面，AI運算需求快速成長，也使CPU重新成為市場競逐焦點。過去以GPU見長的輝達Nvidia( NVDA-US )已推出首款專為AI代理（AI Agent）設計的CPU，積極擴大產品布局，與英特爾及超微AMD( AMD-US )在AI晶片市場展開更激烈競爭。 英特爾近一年來股價也大幅回升。今年6月，執行長陳立武表示，公司目標是在未來5至10年為股東創造10倍報酬，並提出以先進封裝EMIB、玻璃基板，以及氮化鎵（GaN）、碳化矽（SiC）與磷化銦（InP）等新世代半導體材料作為未來技術發展主軸。 其中，英特爾正積極推進EMIB先進封裝技術，並將其定位為對標台積電TSMC( TSM-US )CoWoS先進封裝技術的重要方案；同時也持續布局玻璃基板技術及新材料投資，希望藉由材料創新與先進封裝突破傳統製程微縮逐漸逼近物理極限的發展瓶頸。 隨著AI需求持續帶動高效能運算發展，市場後續將持續觀察CPU價格上漲是否引發其他供應商跟進，以及企業資本支出與PC終端需求是否能支撐目前偏高的硬體價格，同時也將關注英特爾轉型策略能否持續提升其在AI晶片市場的競爭力。 ※ 本文經「優分析」授權轉載，原文出處: 原文連結 ※ 免責聲明：文中所提的個股、基金、期貨商品內容僅供參考，並非投資建議，投資人應獨立判斷，審慎評估風險。 8/11掌握美股科技成長浪潮免費講座 掌握全球財經資訊 點我下載APP ‌ 文章標籤 CPU 半導體 PC 優分析 更多 相關行情 台股首頁 我要存股 英特爾 109.58 -10.3 % 蘋果 312.11 -0.18 % 微軟 389.77 +0.78 % 輝達 196.095 +0.28 % 超微半導體 510.3 -7.56 % 台積電ADR 431.28 -4.54 % 更多 延伸閱讀 超豐電子接手安森美菲律賓廠擴大全球封測版圖 分析師示警：半導體股「高速列車」恐出軌 AI長線趨勢</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6525023</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>英特爾調漲消費與伺服器CPU售價，疊加記憶體漲勢，將直接推升AI建置成本並使PC價格短期內維持高檔。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>博通領軍晶片股走高 美股再創高 道瓊登上53,055點</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>美股 博通領軍晶片股走高 美股再創高 道瓊登上53,055點 優分析 Uanalyze 2026-07-07 09:00 2026年07月07日（優分析／產業數據中心報導）⸺ 美股周一（7月6日）延續強勁走勢，在博通Broadcom( AVGO-US )領軍下，晶片族群全面走揚，帶動投資人持續布局AI概念股，市場也提前押注即將登場的第2季財報季可望繳出亮眼成績。 終場， 道瓊工業指數 上漲155.84點、漲幅0.29%，收在53,055.91點，不僅創下歷史收盤新高，盤中也一度刷新紀錄； 那斯達克綜合指數 大漲1.12%，收26,121.16點；標普500指數上漲0.72%，收7,537.43點。 ‌ 盤面焦點集中在博通Broadcom( AVGO-US )。該公司宣布與蘋果Apple( AAPL-US )延長合作協議，雙方將持續合作開發並供應各式客製化晶片，合約期限延長至2031年，激勵博通股價大漲3.7%。 在博通帶動下，標普500資訊科技類股指數上漲1.3%，先前連續兩個交易日走弱的 費城半導體 指數也反彈2.2%，顯示AI相關晶片族群仍是市場資金追逐的核心。 不過，這波漲勢仍高度集中於少數大型科技股。奧克拉荷馬州Longbow Asset Management執行長Jake Dollarhide表示，目前市場行情主要由特定科技股與半導體股推動，若投資組合未布局相關標的，幾乎難以參與本輪漲勢。他也提醒，這波多頭行情的基礎並不穩固，若聯準會維持高利率的時間長於市場預期，將成為市場最大的風險。 受惠AI晶片需求持續升溫，南韓記憶體大廠SK海力士SK Hynix也將搭上市場熱潮，預計於本周稍晚在 那斯達克 掛牌。 另一方面，微軟Microsoft( MSFT-US )宣布裁員約4,800人，約占全球員工總數2.1%，股價反而下跌近1%，成為大型科技股中表現相對疲弱的個股。 Great Hill Capital董事長Thomas Hayes表示，市場解讀微軟此舉反映公司龐大的資本支出已逐漸受到質疑。投資人認為，公司持續投入大量資金，但回報仍未明顯浮現，如今選擇裁員而非縮減資本支出，因此被視為偏向負面的訊號。 相較之下，戴爾Dell Technologies( DELL-US )股價大漲逾4%。美國總統川普在白宮敲響開市鐘後，公開推薦戴爾電腦產品，帶動市場買盤湧入。 汽車零件通路商O"Reilly Automotive( ORLY-US )則重挫6.7%。彭博先前報導指出，該公司已向同業Genuine Parts( GPC-US )提出現金收購要約，但消息曝光後，Genuine Parts股價也下跌約3%。 此外，馬斯克旗下的SpaceX周一下跌1%，成交金額超過260億美元，且交易多集中於收盤前最後數秒。該公司預計將於周二正式納入 那斯達克 100指數。 經濟數據方面，美國供應管理協會（ISM）公布，6月非製造業採購經理人指數（PMI）由前月略為回落至54.0，符合市場預期，顯示服務業仍維持擴張，但成長動能略有降溫。 隨著美國大型企業將於未來數日陸續公布第2季財報，市場期待持續升溫。根據LSEG I/B/E/S統計，分析師預估標普500成分企業第2季獲利年增率可望達24%，其中科技類股獲利更有望年增約65%。達美航空Delta Air Lines( DAL-US )與百事PepsiCo( PEP-US )都將於本周稍晚公布最新財報。 利率政策方面，上周公布的美國就業報告表現偏冷後，市場對聯準會升息的預期反而升溫。根據芝商所FedWatch工具，市場預估聯準會在7月29日會議升息1碼的機率約25%。 新任聯準會主席Kevin Warsh於上月主持首次會議後，市場普遍認為政策立場較為鷹派，最新會議紀要預計將於周三公布。聯準會理事Christopher Waller周一表示，前瞻指引若運用得宜，可作為加速貨幣政策發揮效果的重要工具，但若使用方式過於僵化，也可能帶來負面影響。 值得注意的是，雖然標普500指數終場收高，但當日下跌家數仍多於上漲家數，比例約為1.3比1，反映市場漲勢仍集中在少數大型權值股。累計今年以來，標普500指數已上漲約10%，但距離6月2日創下的歷史收盤高點仍低約1%。 此外，當日成交量僅168億股，低於過去20個交易日平均的234億股，顯示資金追價態度仍偏向審慎。隨著第2季財報季正式展開，AI相關企業能否持續繳出優於預期的獲利表現，以及聯準會後續政策訊號是否出現變化，將成為影響美股後續走勢與科技股評價的重要觀察重點。 ※ 本文經「優分析」授權轉載，原文出處: 原文連結 ※ 免責聲明：文中所提的個股、基金、期貨商品內容僅供參考，並非投資建議，投資人應獨立判斷，審慎評估風險。 8/11掌握美股科技成長浪潮免費講座 掌握</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6524578</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>美股受博通及AI概念股帶動創高，市場提前押注Q2財報行情，短期資金動能強勁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>台積電衝刺「3兆美元俱樂部」買入時機到了嗎？</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>美股 台積電衝刺「3兆美元俱樂部」買入時機到了嗎？ 鉅亨網新聞中心 2026-07-07 08:30 全球市值達到或超過 3 兆美元的企業目前僅有四家：蘋果 ( AAPL-US )、微軟( MSFT-US )、輝達( NVDA-US ) 和 Alphabet( GOOG-US )。而下一個有望加入 3 兆美元俱樂部的成員台積電( TSM-US )( 2330-TW )，則與上述四家公司截然不同。分析師認為，從當前財務表現來看，3 兆美元大關並不遙遠，台積電的成長路徑清晰可見。 據《智通財經》，蘋果、微軟、輝達和 Alphabet 共同點在於——要麼開發全球最重要的消費性硬體，要麼營運企業賴以生存的軟體基礎設施，要麼設計驅動 AI 革命的晶片。而台積電不生產終端產品，卻為上述公司提供核心元件。截至 2026 年 6 月下旬，台積電市值約 2.24 兆美元，位居全球上市公司市值第六位。 ‌ 2026 年第一季，台積電營收達 359 億美元，年增 40.6%；淨利潤年增 58.3%。毛利率達 66.2%，淨利率高達 50.5%，意味著公司每創造 1 美元營收，就能保留約 0.5 美元作為淨利潤。如此驚人的獲利能力，對絕大多數企業而言幾乎難以想像。 第二季，管理層給出的營收展望為 390 億至 402 億美元。2026 年全年營收（以美元計）預估將成長超過 30%。依照這一趨勢，台積電今年全年營收將遠超 1,500 億美元。若利潤率能維持目前水準，全年獲利規模將相當驚人。 從 2.24 兆美元邁向 3 兆美元，台積電股價約需再上漲 34%。若獲利能維持 50% 甚至更高的年增率，這段差距將快速縮小。 談到 AI 晶片，市場目光幾乎全都聚焦在輝達——這無可厚非。但輝達並不自行製造晶片，AMD、蘋果也是如此。這些公司所有先進處理器，幾乎都出自台積電的晶圓廠。台積電在全球先進晶片製造領域約占 70% 的市占率，在最先進製程方面，目前仍沒有競爭對手能與之匹敵。 目前 7 奈米及以下先進製程已占台積電晶圓營收的 74%。這項產品結構轉變速度極快，而且極為重要，因為先進製程代表更高的晶片單價，也意味著更優異的毛利率。隨著 AI 需求持續推升 3 奈米乃至未來 2 奈米晶片的出貨量，台積電每片晶圓創造的收入將持續提高，獲利能力也將進一步提升。 AI 基礎建設並非一、兩個季度的短期需求。各大超大型雲端服務業者都持續興建龐大的 GPU 運算叢集，而叢集中的每一顆 GPU，都需要台積電代工生產。輝達擁有 Blackwell、亞馬遜擁有 Trainium、Google 擁有 TPU——它們全部都由台積電晶圓廠負責製造。 多年來，投資台積電最大的顧慮一直是地緣政治風險。公司最重要的晶圓廠均位於台灣，因此相關不確定性使分析師在估值時長期給予所謂的「台灣折價」。如今，這項折價正逐漸縮小。 台積電已承諾將向美國亞利桑那州投資 1,650 億美元，規劃興建占地超過 2,000 英畝的園區，包括 6 座晶圓廠、2 座先進封裝廠以及 1 座研發中心。首座亞利桑那州晶圓廠投產第一年便實現 5.14 億美元獲利；第二期廠區將導入 3 奈米製程，預計 2027 年投產，較原定計畫提前整整一年。 隨著更多產能逐步移往美國，本來因地緣政治風險而避開台積電的機構投資人，如今有了重新布局的理由。這項改變的重要性不容小覷——當更多資金追逐同樣優秀的基本面時，不僅有望推升估值倍數，也將與獲利成長形成雙重助力，進一步帶動公司市值攀升。 當然，台積電並非毫無風險。公司高度依賴 ASML 等設備供應商提供最先進製程所需的微影設備，因此仍存在供應鏈依賴。此外，半導體景氣循環也可能反轉。若 AI 基礎建設投資普遍放緩，台積電的業績也將迅速受到影響。 然而，若相信 AI 將是一場持續十年以上的基礎建設浪潮，而且最終仍需要有人製造所有 AI 晶片，那麼台積電邁向 3 兆美元俱樂部的路徑，無疑是目前市場上最具能見度的投資邏輯之一。 8/11掌握美股科技成長浪潮免費講座 掌握全球財經資訊 點我下載APP ‌ 文章標籤 台積電 AI GPU 晶圓 更多 相關行情 台股首頁 我要存股 台積電 2440 -0.81 % 蘋果 312.05 -0.20 % 微軟 389.74 +0.78 % 輝達 196.04 +0.25 % Alphabet公司(C) 364.3104 -0.16 % 台積電ADR 431.185 -4.56 % 更多 鉅亨贏指標 了解更多 # 利多出貨 台積電 53.33 % 勝率 # 動能均線獲利股 台積電 53.33 % 勝率 延伸閱讀 AI投資重心邁向實體產業！高盛：未來6年資本支出或達7.6兆美元 蘋果不放手！博通晶片合作一路延長到2031年 AI熱潮燒不停！SK海力士啟動280億美</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6524472</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>長期</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>台積電財務表現強勁且成長路徑清晰，受惠全球AI硬體需求，具備長期挑戰3兆美元市值的潛力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>《大賣空》貝瑞做空美光有理？《彭博》：AI記憶體超級循環恐迎反轉</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>美股 《大賣空》貝瑞做空美光有理？《彭博》：AI記憶體超級循環恐迎反轉 鉅亨網編譯莊閔棻 2026-07-07 06:40 《彭博》評論認為，以電影《大賣空》原型人物聞名的著名投資人貝瑞（Michael Burry）對記憶體的看法，可能有道理。 根據報導，貝瑞近日在其 Substack 平台發文，宣布放空美光科技 ( MU-US ) 股票，直言美光「是定義景氣循環最典型的案例」。 ‌ 他進一步寫道：「景氣好的時候，這檔股票往往被炒作得遠超過其應有價值；景氣差的時候，又會被市場拋售得遠超過其應有程度。」 分析指出，全球三大記憶體晶片廠，三星電子、SK 海力士與美光的股價表現，充分印證了這個產業長期以來「繁榮與蕭條交替」的宿命。 當獲利大幅成長、前景一片樂觀時，若以預估本益比衡量，這些股票往往顯得異常便宜，吸引部分投資人追高買進，投資行為甚至近似動能交易。 然而，一旦市場情緒轉向悲觀，投資人便會立即質疑分析師的獲利預測可靠性，並開始大舉拋售股票。此時，他們往往改採股價淨值比等估值指標，而這類指標通常較常用於評估陷入困境的企業。 美光於六月底公布亮眼財報後，這場悲喜劇再度上演。歡騰過後隨即是大規模出逃，其中波動性最高的 SK 海力士。因市場擔憂 Meta( META-US ) 與蘋果 ( AAPL-US ) 的採購需求趨緩，該股股價從近期高點重挫最多達 25%。 值得注意的是，美光管理層已積極向市場提供獲利能見度，包括揭露與客戶簽訂的長期合約。 這些合約通常長達五年、附帶預付款機制，且完整履行後可貢獻至少一半營收。然而，市場並不買單，美光股票的遠期本益比已從六月底的 11 倍，滑落至上週收盤的 7 倍。 然而，分析指出，真正的問題並不在於估值指標，或這些股票交易中所隱含的槓桿因素，而是在於記憶體產業本身。這是一個供需關係極其複雜的產業，即使是經驗最豐富的分析師，也可能對市場變化措手不及。 貝瑞認為，南韓的大規模投資計畫是「盛極而衰的開端」。南韓總統李在明日前宣布規模至少達 135 兆 韓元 （約 8,800 億美元）的重大建設計畫，其中包含三星與 SK 海力士在全國西南部新設的晶片廠。 這項計畫雖符合南韓的國家戰略利益，投資規模預計相當於 GDP 的 2.6%，但巴克萊銀行指出，如此快速的產能擴張，將把整個產業的建置規模推升至歷史新高。 屆時，目前應用於 AI 資料中心、智慧型手機及個人電腦的動態隨機存取記憶體（DRAM）供應短缺，最快可能於明年便告結束。 中國的動向同樣不容忽視。遭美國國防部列入黑名單的本土 DRAM 廠商長鑫存儲正籌備上市，計劃募資至少 295 億 人民幣 （約 43 億美元），可能成為中國 2022 年以來最大規模的 IPO 案。 摩根士丹利數據顯示，中國目前佔全球 DRAM 晶圓淨增產量的 30%（至 2028 年），僅次於南韓排名第二。 長鑫存儲的擴張態勢明顯，多年來的投資終見成效，今年首季獲利已突破 200 億 人民幣 。若據報正遊說川普政府降低政治阻力的蘋果最終成為其客戶，長鑫的產能擴張腳步將更為激進。 《彭博》指出，目前三星、SK 海力士與美光掌控全球約 90% 的 DRAM 市場，同時壟斷所有搭配輝達 ( NVDA-US ) GPU 使用的高頻寬記憶體（HBM）晶片生產。然而，這一寡占局面並不穩固。 在 AI 時代，記憶體晶片已被視為戰略資產與財富來源，中國與南韓的政治盤算，隨時可能打亂供需結構。 報導總結稱，半導體分析師近來持續談論由創紀錄獲利與長期客戶合約所推動的「產業超級循環」。然而，當股價估值仍如此劇烈波動，且政治因素足以在一夕之間改變供需格局時，這究竟稱得上是哪一種「超級循環」還是未知數。 《彭博》認為，自 2008 年全球金融危機以來，貝瑞曾多次提出末日式預言，最終都未成真；但這一次，他或許真的說中了。 （本文不開放合作夥伴轉載） 8/11掌握美股科技成長浪潮免費講座 免費體驗5萬美元模擬交易 投資全球資產 掌握全球財經資訊 點我下載APP ‌ 文章標籤 記憶體 大賣空 貝瑞 看空 儲存 中國 南韓 三星 SK海力士 週期 合約 產能 HBM DRAM NAND 供應 擴廠 TOP 更多 相關行情 台股首頁 我要存股 美光科技 920.38 -6.54 % Meta平台 616.56 +2.71 % 蘋果 312.135 -0.17 % 輝達 196.0201 +0.24 % 韓元/美元 0.0007 +0.00 % 人民幣/美元 0.1472 +0.00 % 更多 延伸閱讀 《大賣空》貝瑞放空美光！稱股價恐迎30%修正、警告AI泡沫將破裂 AI的本質是「記憶體」！HBM之父：GPU真正運算的時間只有10% HBF、HBS將接棒 記憶體股暴跌是錯殺？野村：Meta出租算力、南韓擴產都被「</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6522803</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>著名投資人貝瑞放空美光，指其具高度景氣循環特性，且AI記憶體超級循環恐將反轉，產業面臨估值下修風險。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>〈美股盤後〉晶片股反彈帶動費半那指收高 道瓊首度收盤站上53000點</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>美股 〈美股盤後〉晶片股反彈帶動費半那指收高 道瓊首度收盤站上53000點 鉅亨網編譯陳又嘉 綜合外電 2026-07-07 05:37 美國股市周一 (6 日) 收高，AMD( AMD-US )、博通 (Broadcom)( AVGO-US ) 等晶片股強勢反彈，投資人重新買進 AI 相關企業股票，市場預期這些公司將帶動第二季財報表現亮眼。 標普 500 的資訊科技類股指數上漲 1.3%，而 費城半導體 指數在連續兩個交易日下跌後反彈 2.2%。 ‌ 看準投資人對 AI 晶片股的龐大需求，南韓記憶體大廠 SK 海力士 (SK Hynix) 預計本周在 那斯達克 上市。 SpaceX( SPCX-US ) 股價下跌 1%。當天成交金額超過 260 億美元，且大部分交易集中在收盤最後幾秒。市場預期 SpaceX 將於周二正式納入 那斯達克 100 指數。 截至目前， 標普 500 指數 年初至今已上漲約 10%，但距離 6 月 2 日創下的歷史收盤高點仍低約 1%。 美國大型企業即將開始公布第二季財報，投資人抱持高度期待。根據 LSEG I/B/E/S，分析師預估，標普 500 整體企業第二季獲利預計年增 24%。科技類股獲利則預估躍增約 65%。 根據 CME FedWatch 工具，受到上周公布、低於市場預期的就業報告影響，交易員目前認為，聯準會 (Fed) 在 7 月 29 日會議升息 1 碼的機率約為 25%。 先前在新任主席華許 (Kevin Warsh) 主持的首次會議後，市場一度提高了對鷹派政策的預期。此次會議紀錄將於周三公布。 經濟數據方面，美國供應管理協會 (ISM) 公布，6 月非製造業指數由 5 月的 54.5 小幅降至 54.0，與市場預期一致。 美股周一 (6 日) 主要指數表現： 道瓊指數 上漲 155.84 點，或 0.29%，收 53,055.91 點。 那斯達克 指數上漲 288.49 點，或 1.12%，收 26,121.16 點。 S&amp;P 500 指數上漲 54.19 點，或 0.72%，收 7,537.43 點。 費城半導體 指數上漲 273.92 點，或 2.17%，收 12,900.14 點。 NYSE FANG + 指數上漲 187.69 點，或 1.10%，收 17,288.33 點。 標普 500 指數中大型科技股多收漲。(圖片：finviz) 焦點個股 NYSE FANG + 科技五天王多收高。Meta ( META-US ) 上漲 2.98%；蘋果 ( AAPL-US ) 上漲 1.31%；Alphabet ( GOOGL-US ) 上漲 1.82%；微軟 ( MSFT-US ) 下跌 0.96%；亞馬遜 ( AMZN-US ) 上漲 0.61%。 費半 成分股齊漲。輝達 ( NVDA-US ) 上漲 0.37%；博通 ( AVGO-US ) 上漲 3.73%；美光 ( MU-US ) 上漲 0.94%；高通 ( QCOM-US ) 勁揚 5.8%；應用材料 ( AMAT-US ) 下跌 1.7%；德儀 ( TXN-US ) 上漲 3.56%；AMD ( AMD-US ) 大漲 6.61%。 台股 ADR 收紅。台積電 ADR ( TSM-US ) 上漲 3.99%；日月光 ADR ( ASX-US ) 上漲 4.5%；聯電 ADR ( UMC-US ) 勁揚 5.26%；中華電信 ADR ( CHT-US ) 上漲 0.25%。 企業新聞 微軟宣布新一波組織重整，在 AI 投資持續擴大下，將裁減 4,800 名員工，約占全球員工總數 2.1%。遊戲業務 Xbox 為此次改革重心，未來一年將裁撤 3,200 人，約占部門人力兩成。消息影響股價收跌進 1%。 博通宣布已與蘋果將客製化晶片合作協議延長至 2031 年，雙方將持續共同開發並供應客製化晶片，進一步鞏固長期合作關係，也有助於緩解市場對蘋果逐步自研晶片、可能降低對博通依賴的疑慮。 戴爾科技 (Dell Technologies)( DELL-US ) 股價大漲超過 4%。美國總統川普周一在白宮敲響美股開盤鐘後，公開展示並推薦戴爾的電腦產品，激勵股價走高。 華爾街分析 Longbow Asset Management 執行長 Jake Dollarhide 表示，「目前的市場讓很多投資人被甩在後面。如果你沒持有某些科技股、沒有投資半導體，那基本上就錯過了整波漲勢。我認為這是一波相當脆弱的行情。市場仍有風險，尤其是如果聯準會持續維持高利率更久的政策。」 Ameriprise Financial 市場策略師 Anthony Saglimbene 認為，「市場目前的期待非常高，因此我不確定這些股票在下半年是否還能像上半年那樣大漲</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6524274</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>短期</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AI晶片股強勢反彈，投資人預期第二季財報亮眼，帶動美股主要指數創高，市場情緒樂觀。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>美股漲勢過度集中？三大儲存晶片股扛起標普25%漲幅 下半年迎財報大考</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>美股 美股漲勢過度集中？三大儲存晶片股扛起標普25%漲幅 下半年迎財報大考 鉅亨網新聞中心 2026-07-07 05:00 美國股市今年持續走高，不過最新研究顯示，推升大盤的重要力量正高度集中於少數儲存晶片股。根據彭博策略師 Simon White 測算，今年以來， 標普 500 指數 近四分之一的漲幅，來自於 美光科技 ( MU-US ) 、** 閃迪 ( SNDK-US ) 及 西部數據 ( WDC-US )** 三家儲存晶片廠商的股價表現，顯示 AI 投資熱潮下，市場資金正高度集中於特定族群。 （圖：REUTERS/TPG） Simon White 指出，在過去六個月期間， 標普 500 指數 累計上漲 8.3%，其中美光單一公司便貢獻約 1.4 個百分點，約占整體漲幅近六分之一；若將閃迪與西部數據納入計算，三家公司合計對 標普 500 指數 貢獻接近四分之一的報酬，凸顯少數儲存晶片股已成為今年美股上漲的重要支柱。 ‌ 市場人士指出，這也意味著標普 500 今年的漲勢在相當程度上建立於少數個股之上，指數結構集中度明顯提高。隨著分析師對企業獲利預估持續上修的空間逐漸縮小，這些公司未來股價若要延續強勢，將更依賴實際財報表現，而非估值持續擴張。 事實上，今年 4 月成為儲存晶片族群表現的重要轉折點。在此之前， 輝達 ( NVDA-US ) 、** 蘋果 ( AAPL-US ) 及 Alphabet( GOOGL-US )** 等大型科技股長期占據 標普 500 指數 漲幅貢獻排行榜前列，儲存晶片企業對整體指數的影響相對有限。 然而，自 4 月起，隨著市場持續上調儲存晶片產業的獲利預期，不僅帶動整體族群股價快速走升，也促使市場重新評估 AI 供應鏈各環節的受惠程度。投資人逐步區分雲端服務業者與硬體供應商的投資價值，資金開始加速流向儲存晶片廠，使相關個股一度跑贏運算晶片族群。 不過，支撐儲存晶片股大漲的主要因素，如今已出現降溫跡象。彭博統計顯示，標普 500 成分股未來一年每股盈餘 (EPS) 預估的分析師上調與下調比率，目前已回落至約 1 的平衡水準，代表上調家數與下調家數大致相當；未來兩年及三年的獲利預估，上修速度也同步放緩。 分析認為，這代表過去支撐儲存晶片股估值快速提升的預期紅利正在逐漸消退，市場投資邏輯已由「獲利預估持續調升」逐步轉向「實際財報能否兌現預期」。在市場已反映高度樂觀預期的情況下，一旦企業獲利未達預估，股價恐將面臨更大的修正壓力。 此外，儲存晶片的強勢表現，也反映 AI 投資主軸內部正出現新的輪動趨勢。在半導體族群連續領漲近兩年後，市場開始重新評估 AI 價值鏈中不同產業的成長潛力。 彭博分析指出，近期軟體族群已逐漸展現相對優勢，若技術面、企業庫藏股買回規模以及相對動能持續改善，市場資金未來有望進一步流向軟體產業。另一方面，儲存晶片股近期已開始出現階段性拉回，雖然不影響其今年對 標普 500 指數 漲幅的重大貢獻，但也反映高度依賴少數明星股推動的指數結構仍具有一定脆弱性。 展望下半年，市場普遍認為， 標普 500 指數 能否延續漲勢，將高度取決於儲存晶片企業是否能以持續成長的獲利支撐目前偏高的估值。若財報表現未能符合市場期待，今年推升美股的重要動能，未來也可能成為市場波動加劇的主要來源。 8/11掌握美股科技成長浪潮免費講座 免費體驗5萬美元模擬交易 投資全球資產 掌握全球財經資訊 點我下載APP ‌ 文章標籤 科技 美股 儲存 晶片 更多 相關行情 台股首頁 我要存股 S&amp;P 500 7490.84 -0.62 % 美光科技 919.89 -6.59 % Sandisk Corporation 1590.295 -8.84 % 威騰電子 528.36 -8.50 % 輝達 196 +0.23 % 蘋果 311.925 -0.24 % Alphabet公司(A) 367.425 +0.26 % 更多 延伸閱讀 安森美出售菲律賓封測廠 超豐電子接手助其降成本 大摩喊買雲端業者！警告「記憶體」類似「白銀」已見頂 高盛警告「買入一切AI」時代結束！避險基金連4週拋售科技股 馬斯克衝人形機器人 產業高層：「訂閱」才更賺錢 ‌ 鉅亨講座 看更多 講座 公告 上一篇 SK海力士更新美股招股書 半導體設備股聞風而動 下一篇 AI晶片股迎報復性反彈？財經名嘴Jim Cramer喊話重新進場 0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6524415</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>正面</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>中期</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AI熱潮促使資金高度集中美股三大儲存晶片股，下半年財報將是驗證中期估值與支撐漲勢的關鍵。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>〈美股盤後〉美光跌近6%記憶體族群拖累科技股 那指標普連二跌</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>美股 〈美股盤後〉美光跌近6%記憶體族群拖累科技股 那指標普連二跌 鉅亨網編譯陳又嘉 綜合外電 2026-05-19 05:41 美國股市周一 (18 日) 多收低，受科技股走弱拖累，其中記憶體晶片股跌勢尤其明顯。投資人持續關注油價與公債殖利率走勢，同時等待中東衝突的進一步發展。 標普500與那斯達克綜合指數連續第二個交易日下跌(圖：Reuters/TPG) 標普 500 與 那斯達克綜合指數 皆連續第二個交易日下跌。 道瓊工業指數 則上漲 159.95 點，漲幅 0.32%。 ‌ 記憶體晶片類股遭遇拋售潮，起因於希捷科技 (Seagate Technology)( STX-US ) 執行長在摩根大通 (JPMorgan) 會議上表示，新建工廠「耗時太久」。該公司股價重挫近 7%，並拖累同業美光 (Micron Technology)( MU-US ) 下跌近 6%。市場擔憂記憶體產業產能不足，恐無法滿足快速成長的需求，進一步加劇賣壓。 除美光與希捷科技外，威騰電子 (Western Digital)( WDC-US ) 下跌 4.8%，Sandisk 下跌 5.3%。其他 AI 概念股也同步走弱，包括輝達 (Nvidia)( NVDA-US ) 與博通 (Broadcom)( AVGO-US ) 皆下跌約 1%。 這波跌勢發生之際，美股先前才剛創下新高。標普 500 與 那斯達克 上周刷新歷史紀錄， 道瓊指數 也一度重返 50,000 點關卡。 不過，上周五全球主權債殖利率攀升，使主要指數承壓。美國 30 年期公債殖利率升至約一年高點， 10 年期公債殖利率 也維持高檔。英國 30 年期公債殖利率升至 1990 年代末以來最高，日本長天期公債殖利率同樣攀升。 伊朗與美國的緊張局勢仍未緩解，油價維持高檔，市場對衝突後續發展仍缺乏明確方向。西德州中級原油 (WTI) 期貨上漲約 3%，收在每桶 108.66 美元； 布蘭特原油 (Brent) 則上漲逾 2%，收在每桶 112.10 美元。 不過，在美國總統川普於 Truth Social 發文表示，原定周二對伊朗的攻擊行動將暫緩後，油價漲勢有所降溫。川普指出，卡達、沙烏地阿拉伯與阿拉伯聯合大公國領導人要求暫停行動，因為目前「正進行嚴肅談判」，可能達成一項「美國可接受」的協議。 此外，上周公布的通膨數據高於預期，讓市場認為聯準會 (Fed) 短期內降息的可能性大幅降低。 根據芝商所 (CME)FedWatch 工具，交易員目前預估聯準會今年底前升息 25 個基點的機率為 37.8%，反映市場消化上周高於預期的通膨數據。 全球市值最高公司輝達將於周三公布財報。市場對其表現抱持高度期待，該公司股價自 3 月低點以來已大幅反彈，而 費城半導體 指數今年也因 AI 晶片需求強勁而大漲。 全球最大零售商沃爾瑪 (Walmart)( WMT-US ) 本周也將公布財報，市場將藉此觀察美國消費者在高油價與整體通膨壓力下的消費狀況。 美股周一 (18 日) 主要指數表現： 道瓊指數 上漲 159.95 點，或 0.32%，收 49,686.12 點。 那斯達克 指數下跌 134.41 點，或 0.51%，收 26,090.73 點。 S&amp;P 500 指數下跌 5.45 點，或 0.074%，收 7,403.05 點。 費城半導體 指數下跌 285.95 點，或 2.47%，收 11,302.52 點。 NYSE FANG + 指數下跌 139.44 點，或 0.81%，收 17,106.12 點。 標普 11 大類股中，資訊科技類股跌幅最大，其中晶片股為主要拖累，能源類股則表現最佳。(圖片：finviz) 焦點個股 NYSE FANG + 科技五天王漲跌互見。Meta ( META-US ) 下跌 0.49%；蘋果 ( AAPL-US ) 下跌 0.8%；Alphabet ( GOOGL-US ) 上漲 0.04%；微軟 ( MSFT-US ) 上漲 0.38%；亞馬遜 ( AMZN-US ) 上漲 0.27%。 費半 成分股倒一片。輝達 ( NVDA-US ) 下跌 1.33%；博通 ( AVGO-US ) 下跌 1.05%；美光 ( MU-US ) 下跌 5.95%；高通 ( QCOM-US ) 上漲 1.07%；應用材料 ( AMAT-US ) 下跌 5.28%；德儀 ( TXN-US ) 下跌 0.7%；AMD ( AMD-US ) 下跌 0.73%。 台股 ADR 多收低。台積電 ADR ( TSM-US ) 下跌 2.08%；日月光 ADR ( ASX-US ) 下跌 6.39%；聯電 ADR ( UMC-US ) 下跌 0.47%；中華電信 ADR ( CHT-US ) 上漲 0.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6462566</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>美股 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單 鉅亨網編輯林羿君 2026-05-18 22:30 根據最新的財產申報資料，美國總統川普在今年第一季的投資標的中，除了納入輝達 ( NVDA-US ) 、亞馬遜 ( AMZN-US ) 與蘋果 ( AAPL-US ) 等股市巨頭之外，他還入股了一家市值達 6 億美元的迴轉壽司連鎖品牌。 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單。(圖:shutterstock) 川普於 2 月 2 日買進美國藏壽司 ( KRUS-US ) 的股票，交易金額介於 100 萬至 500 萬美元之間。該餐飲集團是由日本藏壽司（Kura Sushi）所控股。 ‌ 與歷任總統的做法不同，川普並未選擇處分自身資產，也未將其移交給獨立監理人進行盲目信託。 申報文件揭露，川普或其投資顧問在首季進行了超過 3,700 筆交易，這使得外界對於川普政府可能涉及「利益衝突」的疑慮再度升溫。 對此，川普集團發言人表示，總統的所有資產均由第三方金融機構獨立管理，並全權負責所有投資決策，不論是川普本人、其家人或集團，皆未參與任何交易決定。 這筆出人意料的投資在日本引發了廣泛熱議，許多網友紛紛在社群平台 X 上猜測，川普本人到底有沒有吃過握壽司。 三菱日聯 eSmart 證券市場分析師山田勉指出，美國藏壽司的營運表現一直以來都極為強勁，而川普入股的消息，可能會進一步刺激東京股市的散戶大舉買進藏壽司股票。 受此消息激勵，在東京掛牌的藏壽司股價於週一 (18 日) 盤中一度大漲 5.4%，創下 2025 年 6 月以來最大的單日盤中漲幅。 而根據該公司的年度有價證券報告，截至去年 10 月底，母公司日本藏壽司持有美國藏壽司約 67% 的表決權。 主動選股績效夯！專家配置一鍵打包 掌握全球財經資訊 點我下載APP ‌ 文章標籤 川普投顧 川普持股 藏壽司 迴轉壽司 TOP 更多 相關行情 台股首頁 我要存股 輝達 222.32 -1.33 % 亞馬遜 264.86 +0.27 % 蘋果 297.84 -0.80 % Kura Sushi USA Inc - Class A 51.07 +1.21 % 更多 延伸閱讀 美以很快再發動攻擊？川普威脅伊朗恐「將一無所有」伊方：美方毫無實質讓步 川普發文警告：如果伊朗不迅速行動 將一無所有 川普警告時間不多 美以密談聯手空襲伊朗 ‌ 鉅亨講座 看更多 講座 公告 上一篇 搶攻AI資料中心商機！NextEra砸668億美元收購Dominion 創電力業紀錄 下一篇 債市已發出警告 但股市投資者尚未計價通膨飆升的風險 0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6462385</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>美股 瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機 鉅亨網編譯段智恆 2026-05-18 20:10 蘋果 ( AAPL-US ) 向來以高單價、高毛利產品聞名，但在全球消費電子成本持續攀升之際，蘋果近年卻成功在平價裝置市場殺出新路，而背後一項關鍵策略，如今也逐漸浮上檯面：將原本可能報廢的「次級晶片」重新利用，轉化為獲利來源。 瑕疵晶片變搖錢樹！蘋果MacBook Neo熱賣背後有玄機(圖：REUTERS/TPG) 根據《華爾街日報》(WSJ)報導，蘋果近期推出售價 599 美元的入門筆電 MacBook Neo，上市後銷售表現優於預期，成為市場熱門產品。不過，支撐這款新產品的核心晶片，並非全新設計，而是兩年前首次搭載於 iPhone 16 Pro 的 A18 Pro 晶片，只是其中圖形處理器 (GPU) 由原本 6 核心降為 5 核心。 ‌ 這意味著，部分在生產過程中未完全達到最高規格、但仍可正常運作的晶片，經過關閉瑕疵核心後，仍能被重新部署至不同產品線，從原本旗艦手機轉向價格更親民的筆電產品。 報導指出，這種做法在半導體業被稱為「分級晶片」(Binned Chips)，透過將晶片依性能分級，區分為高、中、低不同等級，再搭配不同產品定位出售，類似航空座位、飯店房型或鑽石分級的商業模式。 分析人士指出，蘋果近年已將這項原本用於降低報廢率的供應鏈策略，進一步發展為產品設計核心，不僅有效降低成本，也讓蘋果能更精準切分高階與入門市場，吸引更多原本可能選擇 Chromebook、Windows PC 或 Android 手機的消費者。 根據《華爾街日報》分析蘋果近 200 份技術文件，自 2021 年以來，蘋果至少已有 6 款 A 系列晶片，在旗艦 iPhone 首發後，再以少一個 GPU 核心的版本導入較低價產品，包括 iPhone 17e、iPhone Air，以及最新的 MacBook Neo。 Neo 熱銷甚至已消耗完原本庫存的次級晶片。知情人士透露，蘋果近期已向台積電 ( TSM-US )( 2330-TW ) 追加 A18 Pro 晶片訂單，以維持 Neo 產線供應，顯示市場需求遠超預期。 不過，隨著人工智慧 (AI) 晶片需求爆發，全球先進製程產能日益吃緊，台積電供應壓力也同步升高。天風國際證券分析師郭明錤指出，蘋果過去在晶片供應上的彈性優勢正在縮小，相關壓力已開始浮現。蘋果執行長庫克近期也坦言，晶片短缺正影響產品供貨，目前官網顯示 MacBook Neo 出貨時間已延長至 1 至 2 周。 主動選股績效夯！專家配置一鍵打包 免費體驗5萬美元模擬交易 投資全球資產 掌握全球財經資訊 點我下載APP ‌ 文章標籤 蘋果 Apple MacBook Neo A18 Pro GPU 晶片 台積電 庫克 郭明錤 AI 人工智慧 筆電 iPhone 半導體 供應鏈 消費電子 科技 產業 TOP 更多 相關行情 台股首頁 我要存股 台積電 2240 -1.10 % 蘋果 297.84 -0.80 % 台積電ADR 395.95 -2.08 % 更多 延伸閱讀 川普自曝入股英特爾談判內幕：早知道應該多要一點 2兆美元值不值？SpaceX IPO背後的FOMO心理學 輝達法說不只看財報！市場更想聽黃仁勳談川普與對中晶片出口 Meta裁員不只是省錢！祖克柏AI重押正改變矽谷生態 ‌ 鉅亨講座 看更多 講座 公告 上一篇 川普首季持股驚見「藏壽司」 日本股價急噴、散戶瘋跟單 下一篇 債券拋售加劇 美股恐迎「首波實質修正」威脅AI漲勢 0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://news.cnyes.com/news/id/6462511</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>鉅亨網-美股-AAPL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>